--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC669D19-5121-4B68-B23A-09ACFA85D764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00E03FF-9BC9-4D0D-BF7E-0CAE5792AEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
   <si>
     <t>調整label設定後</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,14 +141,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>直接用feature差異訓練fuzzy detector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>用feature的shap簽名差異訓練fuzzy detector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.7567</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -198,6 +190,134 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用feature(128)的shap簽名差異訓練fuzzy detector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用feature(logit)的shap簽名差異訓練fuzzy detector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9633</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9700</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9569</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>626/1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.352</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9467</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9333</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9422</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>43</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>435/1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.222,iter=103</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接用feature(128)差異訓練fuzzy detector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>直接用feature(logit)差異訓練fuzzy detector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8533</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7551</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>781/1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8421</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>623/1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.437 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.253,iter=146 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>63</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -597,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F37ECD-1310-4DB8-985C-13F95F33B97D}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.75" style="1" bestFit="1" customWidth="1"/>
@@ -617,7 +737,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -700,7 +820,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -734,25 +854,25 @@
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -760,30 +880,196 @@
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G11" s="1" t="s">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.25">
-      <c r="I17" s="1" t="s">
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D00E03FF-9BC9-4D0D-BF7E-0CAE5792AEDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9B06C5-D6F9-47FC-B348-1F4A9FE1BA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>調整label設定後</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,10 +61,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> Successful/Total</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Params</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -109,10 +105,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>365/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">eps=0.272 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -133,10 +125,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>473/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">eps=0.234,iter=91 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -157,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>686/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>eps=0.401</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -181,10 +165,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>426/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>eps=0.224,iter=105</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,62 +181,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.9633</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9569</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>51</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6290</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>626/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps=0.352</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9467</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9333</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9422</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>43</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4360</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>435/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps=0.222,iter=103</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>直接用feature(128)差異訓練fuzzy detector</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -265,59 +189,94 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.8533</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9095</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7551</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7810</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>781/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8421</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8032</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6230</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>623/1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">eps=0.437 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">eps=0.253,iter=146 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>61</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>63</t>
+    <t>0.9850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9860</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9799</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>33</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4840</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.297</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9883</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9879</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9846</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.3900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.214,iter=91 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7117</t>
+  </si>
+  <si>
+    <t>0.7343</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>57</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6660</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9260</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6378</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6635</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6450</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.371 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.364,iter=130</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -717,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F37ECD-1310-4DB8-985C-13F95F33B97D}">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.75" style="1" bestFit="1" customWidth="1"/>
@@ -726,26 +685,26 @@
     <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>1</v>
@@ -762,73 +721,64 @@
       <c r="G4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="2" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -845,73 +795,64 @@
       <c r="G9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="2" t="s">
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>1</v>
@@ -928,78 +869,69 @@
       <c r="G14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="2" t="s">
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="H17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="I17" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>1</v>
@@ -1016,60 +948,51 @@
       <c r="G19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="H20" s="1" t="s">
+      <c r="F21" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9B06C5-D6F9-47FC-B348-1F4A9FE1BA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D67540-0031-45A5-947C-159C1312A430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
   <si>
     <t>調整label設定後</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -189,50 +189,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.9850</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9860</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9799</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>33</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4840</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps=0.297</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9883</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.9879</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.9846</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.3900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">eps=0.214,iter=91 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.7117</t>
   </si>
   <si>
@@ -278,6 +238,48 @@
   <si>
     <t>eps=0.364,iter=130</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8610</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8780</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8502</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7650</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9880</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9826</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8760</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.343,iter=142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.446 </t>
   </si>
 </sst>
 </file>
@@ -875,22 +877,22 @@
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -898,22 +900,22 @@
         <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -954,22 +956,22 @@
         <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -977,22 +979,22 @@
         <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D67540-0031-45A5-947C-159C1312A430}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F1665C-23C8-4F76-BE20-E21DAF397502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
   <si>
     <t>調整label設定後</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -280,6 +280,92 @@
   </si>
   <si>
     <t xml:space="preserve">eps=0.446 </t>
+  </si>
+  <si>
+    <t>0.5100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5923</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>38</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8530</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8870</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7699</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7681</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7820</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5850</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5464</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5656</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.258 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.235,iter=109 </t>
+  </si>
+  <si>
+    <t>0.9250</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7561</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7573</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7660</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5564</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -678,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F37ECD-1310-4DB8-985C-13F95F33B97D}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.75" style="1" bestFit="1" customWidth="1"/>
@@ -688,20 +774,28 @@
     <col min="5" max="5" width="7.375" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="8" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="17.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -724,7 +818,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -747,7 +841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -770,12 +864,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -798,7 +892,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
@@ -821,7 +915,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>10</v>
       </c>
@@ -844,12 +938,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -871,8 +965,29 @@
       <c r="G14" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
@@ -894,8 +1009,29 @@
       <c r="G15" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="J15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
@@ -917,18 +1053,39 @@
       <c r="G16" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H17" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -950,8 +1107,29 @@
       <c r="G19" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
@@ -973,8 +1151,29 @@
       <c r="G20" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -995,6 +1194,27 @@
       </c>
       <c r="G21" s="1" t="s">
         <v>59</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9F1665C-23C8-4F76-BE20-E21DAF397502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E535E471-AFEC-4E62-BA40-A88F4226EAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,11 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
-  <si>
-    <t>調整label設定後</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
   <si>
     <t>F1-Score</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -181,10 +177,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>直接用feature(128)差異訓練fuzzy detector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>直接用feature(logit)差異訓練fuzzy detector</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -282,89 +274,103 @@
     <t xml:space="preserve">eps=0.446 </t>
   </si>
   <si>
-    <t>0.5100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5923</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>38</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8530</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8870</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7699</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7681</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7820</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5850</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5464</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5656</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>59</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">eps=0.258 </t>
   </si>
   <si>
     <t xml:space="preserve">eps=0.235,iter=109 </t>
   </si>
   <si>
-    <t>0.9250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>54</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7561</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7573</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7660</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.5564</t>
+    <t>0.5680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5894</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5730</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9230</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9320</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>51</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8311</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.336 </t>
+  </si>
+  <si>
+    <t>eps=0.252,iter=117</t>
+  </si>
+  <si>
+    <t>0.6670</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6751</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6583</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9240</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9390</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>53</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7808</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8063</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MINST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CIFAR10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用feature(128)差異訓練fuzzy detector</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -372,7 +378,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -395,6 +401,14 @@
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -420,7 +434,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -430,11 +444,182 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -445,6 +630,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}" name="表格1" displayName="表格1" ref="A16:G18" totalsRowShown="0" headerRowDxfId="24">
+  <autoFilter ref="A16:G18" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{2D05F2D9-4E34-4B8C-BF61-15BC77447128}" name="Attack               " dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{E5C65CAB-E14F-4DB5-BC72-383960132775}" name=" Detection(accuracy)" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{3F6053E5-F1AF-447A-85FF-925B92FBCD45}" name="F1-Score" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{810D88D6-665F-4538-9A15-800A2D94FB56}" name="AUC" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{CDA6439C-BA9F-4FF9-9F6D-4B199B84E20A}" name=" Rules" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{CB91E04A-FFAC-4CB9-A071-301522257764}" name=" Success Rate" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{68770955-8134-421F-BE0C-CA1768ED7677}" name="Params" dataDxfId="25"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}" name="表格2" displayName="表格2" ref="A21:G23" totalsRowShown="0" headerRowDxfId="16">
+  <autoFilter ref="A21:G23" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{061A4045-4D20-4690-BF90-F037B6A084FD}" name="Attack               " dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{3E67C7DF-C7F4-41BF-9E0C-7B4E7BB5436E}" name=" Detection(accuracy)" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{E1C58D53-2D93-433C-98C0-8100DFEBEB1C}" name="F1-Score" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{F3B2873D-A702-445F-BBF4-A9E9BF65522D}" name="AUC" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{172D76D0-6A3C-4F55-99D3-7BC387FCF56F}" name=" Rules" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{0FDC5BAF-85F9-47FE-860B-15BF2DC53F1D}" name=" Success Rate" dataDxfId="18"/>
+    <tableColumn id="7" xr3:uid="{94F7DF17-E030-4CB7-A4ED-AB3EC2E97371}" name="Params" dataDxfId="17"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}" name="表格3" displayName="表格3" ref="J16:P18" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="J16:P18" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{30237086-6922-4840-9E1F-E061F0031A87}" name="Attack               " dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{D49B86DE-B635-481D-8492-2261ED37C684}" name=" Detection(accuracy)" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{C13E86B0-B7CF-4A76-BB9A-3B370A1FDD39}" name="F1-Score" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{D048EC23-8F5B-4186-88C7-F59AD8F86137}" name="AUC" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{1DC2BDCC-9CCD-42DD-90FA-E9F26AC10F55}" name=" Rules" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{AE35ABC0-745F-4728-988B-1105CF016F33}" name=" Success Rate" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{A25FB374-3BF1-4235-8D96-2E0420E7DAD4}" name="Params" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}" name="表格4" displayName="表格4" ref="J21:P23" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="J21:P23" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{009D9A0D-280E-4068-BE4F-605CE1915EE9}" name="Attack               " dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C82BB803-BC93-4AF1-B28C-54286B70BE4B}" name=" Detection(accuracy)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{540DB8D8-692F-4F7E-BF1F-0D40C69C1E4A}" name="F1-Score" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{BEDCE635-46F2-42D2-9FB9-07489CB2CD10}" name="AUC" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{1956482D-F85D-4657-852D-1AE84D82FE74}" name=" Rules" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{3476352A-8AB8-4EE3-B2C8-DFE8F426B503}" name=" Success Rate" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{ADA50542-F144-4686-A5E3-B5EC564F8625}" name="Params" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -764,461 +1013,486 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F37ECD-1310-4DB8-985C-13F95F33B97D}">
-  <dimension ref="A1:P21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:P23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="17.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19" style="1" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
+    <col min="12" max="12" width="11.109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="8.77734375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="15.5546875" style="1" customWidth="1"/>
+    <col min="16" max="16" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="D4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="H19" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="D23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="H17" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="1" t="s">
+      <c r="K23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>76</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="J15:P15"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="4">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/experiment/實驗結果.xlsx
+++ b/experiment/實驗結果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ted\Desktop\論文\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E535E471-AFEC-4E62-BA40-A88F4226EAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CCC992A-5E8C-4B93-B82B-2A28E0BAFFD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3ECA1DB8-1BD9-46FA-B4F1-485F2799EAA5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="142">
   <si>
     <t>F1-Score</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,107 +173,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用feature(logit)的shap簽名差異訓練fuzzy detector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>直接用feature(logit)差異訓練fuzzy detector</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.9879</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7117</t>
-  </si>
-  <si>
-    <t>0.7343</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.7090</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>57</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6660</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.9260</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>56</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6378</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6635</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.6450</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">eps=0.371 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps=0.364,iter=130</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8610</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8780</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.8502</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.7650</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0.9880</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.9826</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>31</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.8760</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>eps=0.343,iter=142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eps=0.446 </t>
-  </si>
-  <si>
     <t xml:space="preserve">eps=0.258 </t>
   </si>
   <si>
@@ -371,6 +286,318 @@
   </si>
   <si>
     <t>用feature(128)差異訓練fuzzy detector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Method</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Threshold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>balanced</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>門檻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EFIS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>equal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logit差異</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>logit+ shap 簽名差異</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6680</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5304</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.015398</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9360</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.349  </t>
+  </si>
+  <si>
+    <t>eps=0.275,iter=103</t>
+  </si>
+  <si>
+    <t>0.104892</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7890</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7640</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.143142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.381 </t>
+  </si>
+  <si>
+    <t>eps=0.212,iter=142</t>
+  </si>
+  <si>
+    <t>0.9290</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6740</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7384</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7386</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7786</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7499</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.767521</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6390</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.126472</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.409</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5970</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6898</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.6328</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.108604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9870</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">eps=0.272,iter=103 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.8010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7925</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7914</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>48</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9210</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.431</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7755</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.7809</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9860</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.268,iter=93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9788</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9789</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9150</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.308</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9810</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9807</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9805</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9980</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.341,iter=142</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9053</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.186900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.342</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9876</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.217303</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.9590</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eps=0.312,iter=146</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -378,7 +605,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -411,6 +638,22 @@
       <family val="1"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="4"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -420,12 +663,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -434,7 +692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -444,17 +702,50 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="68">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -497,6 +788,9 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -538,6 +832,9 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -579,6 +876,9 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -619,6 +919,149 @@
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="新細明體"/>
+        <family val="1"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -633,64 +1076,132 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}" name="表格1" displayName="表格1" ref="A16:G18" totalsRowShown="0" headerRowDxfId="24">
-  <autoFilter ref="A16:G18" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}" name="表格1" displayName="表格1" ref="A31:G33" totalsRowShown="0" headerRowDxfId="67">
+  <autoFilter ref="A31:G33" xr:uid="{4E9E3DA6-33F4-44F0-8241-E96B1F107839}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2D05F2D9-4E34-4B8C-BF61-15BC77447128}" name="Attack               " dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{E5C65CAB-E14F-4DB5-BC72-383960132775}" name=" Detection(accuracy)" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{3F6053E5-F1AF-447A-85FF-925B92FBCD45}" name="F1-Score" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{810D88D6-665F-4538-9A15-800A2D94FB56}" name="AUC" dataDxfId="28"/>
-    <tableColumn id="5" xr3:uid="{CDA6439C-BA9F-4FF9-9F6D-4B199B84E20A}" name=" Rules" dataDxfId="27"/>
-    <tableColumn id="6" xr3:uid="{CB91E04A-FFAC-4CB9-A071-301522257764}" name=" Success Rate" dataDxfId="26"/>
-    <tableColumn id="7" xr3:uid="{68770955-8134-421F-BE0C-CA1768ED7677}" name="Params" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{2D05F2D9-4E34-4B8C-BF61-15BC77447128}" name="Attack               " dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{E5C65CAB-E14F-4DB5-BC72-383960132775}" name=" Detection(accuracy)" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{3F6053E5-F1AF-447A-85FF-925B92FBCD45}" name="F1-Score" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{810D88D6-665F-4538-9A15-800A2D94FB56}" name="AUC" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{CDA6439C-BA9F-4FF9-9F6D-4B199B84E20A}" name=" Rules" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{CB91E04A-FFAC-4CB9-A071-301522257764}" name=" Success Rate" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{68770955-8134-421F-BE0C-CA1768ED7677}" name="Params" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}" name="表格2" displayName="表格2" ref="A21:G23" totalsRowShown="0" headerRowDxfId="16">
-  <autoFilter ref="A21:G23" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}" name="表格2" displayName="表格2" ref="A36:G38" totalsRowShown="0" headerRowDxfId="59">
+  <autoFilter ref="A36:G38" xr:uid="{FFBF48F0-CD72-47B5-85AA-8425E385F042}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{061A4045-4D20-4690-BF90-F037B6A084FD}" name="Attack               " dataDxfId="23"/>
-    <tableColumn id="2" xr3:uid="{3E67C7DF-C7F4-41BF-9E0C-7B4E7BB5436E}" name=" Detection(accuracy)" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{E1C58D53-2D93-433C-98C0-8100DFEBEB1C}" name="F1-Score" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{F3B2873D-A702-445F-BBF4-A9E9BF65522D}" name="AUC" dataDxfId="20"/>
-    <tableColumn id="5" xr3:uid="{172D76D0-6A3C-4F55-99D3-7BC387FCF56F}" name=" Rules" dataDxfId="19"/>
-    <tableColumn id="6" xr3:uid="{0FDC5BAF-85F9-47FE-860B-15BF2DC53F1D}" name=" Success Rate" dataDxfId="18"/>
-    <tableColumn id="7" xr3:uid="{94F7DF17-E030-4CB7-A4ED-AB3EC2E97371}" name="Params" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{061A4045-4D20-4690-BF90-F037B6A084FD}" name="Attack               " dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{3E67C7DF-C7F4-41BF-9E0C-7B4E7BB5436E}" name=" Detection(accuracy)" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{E1C58D53-2D93-433C-98C0-8100DFEBEB1C}" name="F1-Score" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{F3B2873D-A702-445F-BBF4-A9E9BF65522D}" name="AUC" dataDxfId="55"/>
+    <tableColumn id="5" xr3:uid="{172D76D0-6A3C-4F55-99D3-7BC387FCF56F}" name=" Rules" dataDxfId="54"/>
+    <tableColumn id="6" xr3:uid="{0FDC5BAF-85F9-47FE-860B-15BF2DC53F1D}" name=" Success Rate" dataDxfId="53"/>
+    <tableColumn id="7" xr3:uid="{94F7DF17-E030-4CB7-A4ED-AB3EC2E97371}" name="Params" dataDxfId="52"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}" name="表格3" displayName="表格3" ref="J16:P18" totalsRowShown="0" headerRowDxfId="8">
-  <autoFilter ref="J16:P18" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}" name="表格3" displayName="表格3" ref="J31:P33" totalsRowShown="0" headerRowDxfId="51">
+  <autoFilter ref="J31:P33" xr:uid="{12C0EB94-435A-4604-A90F-A55C4D09FDB8}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{30237086-6922-4840-9E1F-E061F0031A87}" name="Attack               " dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{D49B86DE-B635-481D-8492-2261ED37C684}" name=" Detection(accuracy)" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{C13E86B0-B7CF-4A76-BB9A-3B370A1FDD39}" name="F1-Score" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{D048EC23-8F5B-4186-88C7-F59AD8F86137}" name="AUC" dataDxfId="12"/>
-    <tableColumn id="5" xr3:uid="{1DC2BDCC-9CCD-42DD-90FA-E9F26AC10F55}" name=" Rules" dataDxfId="11"/>
-    <tableColumn id="6" xr3:uid="{AE35ABC0-745F-4728-988B-1105CF016F33}" name=" Success Rate" dataDxfId="10"/>
-    <tableColumn id="7" xr3:uid="{A25FB374-3BF1-4235-8D96-2E0420E7DAD4}" name="Params" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{30237086-6922-4840-9E1F-E061F0031A87}" name="Attack               " dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{D49B86DE-B635-481D-8492-2261ED37C684}" name=" Detection(accuracy)" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{C13E86B0-B7CF-4A76-BB9A-3B370A1FDD39}" name="F1-Score" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{D048EC23-8F5B-4186-88C7-F59AD8F86137}" name="AUC" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{1DC2BDCC-9CCD-42DD-90FA-E9F26AC10F55}" name=" Rules" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{AE35ABC0-745F-4728-988B-1105CF016F33}" name=" Success Rate" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{A25FB374-3BF1-4235-8D96-2E0420E7DAD4}" name="Params" dataDxfId="44"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}" name="表格4" displayName="表格4" ref="J21:P23" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="J21:P23" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}" name="表格4" displayName="表格4" ref="J36:P38" totalsRowShown="0" headerRowDxfId="43">
+  <autoFilter ref="J36:P38" xr:uid="{276066A1-87F8-4DFB-B75B-D0D804A17625}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{009D9A0D-280E-4068-BE4F-605CE1915EE9}" name="Attack               " dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{C82BB803-BC93-4AF1-B28C-54286B70BE4B}" name=" Detection(accuracy)" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{540DB8D8-692F-4F7E-BF1F-0D40C69C1E4A}" name="F1-Score" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{BEDCE635-46F2-42D2-9FB9-07489CB2CD10}" name="AUC" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{1956482D-F85D-4657-852D-1AE84D82FE74}" name=" Rules" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{3476352A-8AB8-4EE3-B2C8-DFE8F426B503}" name=" Success Rate" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{ADA50542-F144-4686-A5E3-B5EC564F8625}" name="Params" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{009D9A0D-280E-4068-BE4F-605CE1915EE9}" name="Attack               " dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{C82BB803-BC93-4AF1-B28C-54286B70BE4B}" name=" Detection(accuracy)" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{540DB8D8-692F-4F7E-BF1F-0D40C69C1E4A}" name="F1-Score" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{BEDCE635-46F2-42D2-9FB9-07489CB2CD10}" name="AUC" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{1956482D-F85D-4657-852D-1AE84D82FE74}" name=" Rules" dataDxfId="38"/>
+    <tableColumn id="6" xr3:uid="{3476352A-8AB8-4EE3-B2C8-DFE8F426B503}" name=" Success Rate" dataDxfId="37"/>
+    <tableColumn id="7" xr3:uid="{ADA50542-F144-4686-A5E3-B5EC564F8625}" name="Params" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{BD9D5B44-D6F7-4F18-A3BB-69E3DDE08D3E}" name="表格1_7" displayName="表格1_7" ref="A21:H23" totalsRowShown="0" headerRowDxfId="35">
+  <autoFilter ref="A21:H23" xr:uid="{BD9D5B44-D6F7-4F18-A3BB-69E3DDE08D3E}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{AA1826C9-6D0E-490E-91A9-5B8379635781}" name="Attack               " dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{408C9A62-93C3-4DBB-9CE4-768570BCB2C3}" name=" Detection(accuracy)" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{7A75C459-11D9-4D5C-82C8-ED3F58E4A278}" name="F1-Score" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{260770D1-D880-4453-A8ED-7B0E2F78FB36}" name="AUC" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{BDB868CC-3FAC-4D01-803F-DD7A1B8C9B74}" name="Method" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{688D83D0-93F3-48D1-950A-307097EBA359}" name="Threshold" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{5EFF785A-820C-43E8-9DED-1E38BB560C04}" name=" Success Rate" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{5EB02ABB-FEDF-40BA-BFAF-9BE9109C3F98}" name="Params" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{938D10A8-4C99-4E4E-B5D8-FA6318D06763}" name="表格1_710" displayName="表格1_710" ref="A26:H28" totalsRowShown="0" headerRowDxfId="26">
+  <autoFilter ref="A26:H28" xr:uid="{938D10A8-4C99-4E4E-B5D8-FA6318D06763}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{B6A98BB4-6A55-4A70-990A-39BFD188BB42}" name="Attack               " dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{55F9E1EF-2D88-4249-91DB-9A9D792F9A3B}" name=" Detection(accuracy)" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{618D6A4A-9A15-48FE-80D7-876778B59262}" name="F1-Score" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{D393C705-82EF-4D93-915B-A681F0886815}" name="AUC" dataDxfId="22"/>
+    <tableColumn id="8" xr3:uid="{89F9902C-B669-47EA-AC3C-FE067CED6539}" name="Method" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{35CEB808-3309-4FBD-8391-BA19066E2663}" name="Threshold" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{569281AA-0AB4-4A29-91DC-1D570A7D1986}" name=" Success Rate" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{0116AD1D-385E-432E-A669-3F97A1784155}" name="Params" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{52E2BDFF-BC1F-4659-92B4-980D778D82D0}" name="表格1_711" displayName="表格1_711" ref="J21:Q23" totalsRowShown="0" headerRowDxfId="17">
+  <autoFilter ref="J21:Q23" xr:uid="{52E2BDFF-BC1F-4659-92B4-980D778D82D0}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{1ADFCD44-FF5C-4DB8-B787-8E7FE18AC16F}" name="Attack               " dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{ABC294DE-E364-41D1-8AFF-5477FBBC5604}" name=" Detection(accuracy)" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{8FD4E819-C045-4436-8398-D2986522D951}" name="F1-Score" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{0C1C0298-2D68-424E-960B-5B36228F506B}" name="AUC" dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{B1A50409-34A2-4442-B6B4-6B23FEE93F3E}" name="Method" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{BE11E9FB-B697-494B-9EAC-3D4C28D03575}" name="Threshold" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{55EF2E5B-0933-4A3D-8DA2-00A9DA698F77}" name=" Success Rate" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{E3B380F8-ABCC-4B46-A5ED-3943120C9C7F}" name="Params" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E8D862DF-34B9-42EC-B675-75324379A418}" name="表格1_71112" displayName="表格1_71112" ref="J26:Q28" totalsRowShown="0" headerRowDxfId="8">
+  <autoFilter ref="J26:Q28" xr:uid="{E8D862DF-34B9-42EC-B675-75324379A418}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{17DA683E-FD78-485A-AF00-399D6F9FAF89}" name="Attack               " dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{BA397FFE-F2C7-4703-AB14-12AFE0788D92}" name=" Detection(accuracy)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{4CB8B741-24B5-409A-A03B-9B9038C8775D}" name="F1-Score" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{671C329E-93C2-4FC9-B93A-0C05EBA48FCB}" name="AUC" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{0595D375-4D99-4B9E-8AE3-24E3A034AAF4}" name="Method" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{97FB09CE-AB4F-4268-A718-A33198823176}" name="Threshold" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{92456F61-AE3A-4324-8F91-0C2A1405495B}" name=" Success Rate" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{6B712731-9D6F-4170-AEEA-FFE518CAE753}" name="Params" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,33 +1524,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11F37ECD-1310-4DB8-985C-13F95F33B97D}">
-  <dimension ref="A3:P23"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <dimension ref="A3:Q38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19" style="1" customWidth="1"/>
-    <col min="2" max="2" width="22" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="9" style="1"/>
-    <col min="10" max="10" width="19" style="1" customWidth="1"/>
-    <col min="11" max="11" width="22" style="1" customWidth="1"/>
-    <col min="12" max="12" width="11.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.77734375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="8.77734375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.5546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="45.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="1"/>
+    <col min="10" max="10" width="19.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -1062,7 +1575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1085,7 +1598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1108,12 +1621,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
@@ -1136,7 +1649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1159,7 +1672,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,174 +1695,66 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="J15" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K17" s="1" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="J18" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="N18" s="1" t="s">
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="H19" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J20" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>5</v>
       </c>
@@ -1363,12 +1768,15 @@
         <v>1</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>4</v>
       </c>
       <c r="J21" s="2" t="s">
@@ -1384,115 +1792,577 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="O21" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>52</v>
+        <v>101</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>58</v>
+        <v>102</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>8</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="J23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>60</v>
+        <v>34</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="M27" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O32" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="H34" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="J18:P18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
+  <tableParts count="8">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>